--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T12:45:19+00:00</t>
+    <t>2026-07-01T12:47:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T12:47:01+00:00</t>
+    <t>2026-07-01T12:54:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T12:54:09+00:00</t>
+    <t>2026-07-01T13:22:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T13:22:24+00:00</t>
+    <t>2026-07-01T14:12:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T14:12:20+00:00</t>
+    <t>2026-07-01T14:40:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T14:40:37+00:00</t>
+    <t>2026-07-01T14:56:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T14:56:52+00:00</t>
+    <t>2026-07-01T15:06:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T15:06:20+00:00</t>
+    <t>2026-07-02T07:09:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-02T07:09:29+00:00</t>
+    <t>2026-07-02T08:09:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-02T08:09:18+00:00</t>
+    <t>2026-07-02T08:36:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-02T08:36:38+00:00</t>
+    <t>2026-07-02T09:18:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-02T09:18:57+00:00</t>
+    <t>2026-07-02T09:27:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-02T09:27:16+00:00</t>
+    <t>2026-07-02T09:28:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-02T09:28:31+00:00</t>
+    <t>2026-07-02T14:56:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-02T14:56:20+00:00</t>
+    <t>2026-07-02T14:57:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-02T14:57:33+00:00</t>
+    <t>2026-07-02T15:07:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-02T15:07:06+00:00</t>
+    <t>2026-07-02T15:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-02T15:08:41+00:00</t>
+    <t>2026-07-02T15:24:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-02T15:24:43+00:00</t>
+    <t>2026-07-02T15:31:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-02T15:31:57+00:00</t>
+    <t>2026-07-02T15:33:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-02T15:33:01+00:00</t>
+    <t>2026-07-06T07:26:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T07:26:45+00:00</t>
+    <t>2026-07-06T07:32:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T07:32:14+00:00</t>
+    <t>2026-07-06T07:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T07:33:52+00:00</t>
+    <t>2026-07-06T07:45:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T07:45:53+00:00</t>
+    <t>2026-07-06T07:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T07:47:13+00:00</t>
+    <t>2026-07-06T07:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T07:47:49+00:00</t>
+    <t>2026-07-06T08:10:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T08:10:39+00:00</t>
+    <t>2026-07-06T08:32:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T08:32:13+00:00</t>
+    <t>2026-07-06T08:32:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T08:32:48+00:00</t>
+    <t>2026-07-06T08:33:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T08:33:32+00:00</t>
+    <t>2026-07-06T08:33:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T08:33:50+00:00</t>
+    <t>2026-07-06T08:34:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T08:34:25+00:00</t>
+    <t>2026-07-06T08:35:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T08:35:06+00:00</t>
+    <t>2026-07-06T08:36:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T08:36:02+00:00</t>
+    <t>2026-07-06T08:48:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T08:48:45+00:00</t>
+    <t>2026-07-06T11:34:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T11:34:52+00:00</t>
+    <t>2026-07-06T11:39:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T11:39:46+00:00</t>
+    <t>2026-07-07T08:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T08:57:39+00:00</t>
+    <t>2026-07-07T08:59:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T08:59:34+00:00</t>
+    <t>2026-07-07T12:36:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T12:36:06+00:00</t>
+    <t>2026-07-07T12:36:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T12:36:21+00:00</t>
+    <t>2026-07-07T12:59:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T12:59:25+00:00</t>
+    <t>2026-07-07T15:16:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/reorganisation-IG/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T15:16:43+00:00</t>
+    <t>2026-07-07T15:28:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
